--- a/tracking_forms/015_fire_extinguisher_checklist--tracking_forms.xlsx
+++ b/tracking_forms/015_fire_extinguisher_checklist--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'water',_'value':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Water', 'value': 'water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'foam',_'value':_'foam'}</t>
+          <t>foam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Foam', 'value': 'foam'}</t>
+          <t>Foam</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dry',_'value':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dry', 'value': 'dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'partially_extinguished',_'value':_'partially_extinguished'}</t>
+          <t>partially_extinguished</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Partially Extinguished', 'value': 'partially_extinguished'}</t>
+          <t>Partially Extinguished</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'needs_recharge',_'value':_'needs_recharge'}</t>
+          <t>needs_recharge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Needs Recharge', 'value': 'needs_recharge'}</t>
+          <t>Needs Recharge</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'kitchen',_'value':_'kitchen'}</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Kitchen', 'value': 'kitchen'}</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bathroom',_'value':_'bathroom'}</t>
+          <t>bathroom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bathroom', 'value': 'bathroom'}</t>
+          <t>Bathroom</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'office',_'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Office', 'value': 'office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
